--- a/xlsx/12-S1.xlsx
+++ b/xlsx/12-S1.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S71"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -458,7 +458,6 @@
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="4" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,11 +551,6 @@
           <t>诅咒</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>应对方式</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -645,7 +639,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -734,11 +727,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -827,7 +815,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -916,7 +903,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1005,7 +991,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1094,7 +1079,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1183,7 +1167,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1272,7 +1255,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1361,7 +1343,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1450,7 +1431,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1539,7 +1519,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1628,7 +1607,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1717,7 +1695,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1806,7 +1783,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1895,7 +1871,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1984,7 +1959,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2073,7 +2047,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2162,11 +2135,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2255,7 +2223,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2344,7 +2311,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2433,7 +2399,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2522,7 +2487,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2611,7 +2575,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2700,7 +2663,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2789,7 +2751,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2878,7 +2839,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2967,7 +2927,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3056,7 +3015,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3145,7 +3103,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3234,7 +3191,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3323,11 +3279,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>注意眩晕</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3416,11 +3367,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>注意流血（可驱散）</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3509,11 +3455,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>注意激怒（可安抚）</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3602,7 +3543,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3691,11 +3631,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>注意激怒（可安抚）</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3784,7 +3719,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3873,7 +3807,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3962,7 +3895,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4051,7 +3983,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4140,7 +4071,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4229,7 +4159,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -4318,7 +4247,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4407,7 +4335,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4496,7 +4423,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4585,11 +4511,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>注意激怒（可安抚）</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4678,7 +4599,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4767,7 +4687,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4856,7 +4775,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4945,7 +4863,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -5034,7 +4951,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -5123,7 +5039,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -5212,7 +5127,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -5301,7 +5215,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -5390,7 +5303,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -5479,7 +5391,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -5568,7 +5479,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5657,7 +5567,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -5746,11 +5655,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S59" s="2" t="inlineStr">
-        <is>
-          <t>注意流血（可驱散）</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -5839,7 +5743,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5928,7 +5831,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -6017,11 +5919,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S62" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -6110,7 +6007,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -6199,7 +6095,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -6288,7 +6183,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -6377,7 +6271,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -6466,7 +6359,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -6555,7 +6447,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -6644,7 +6535,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -6733,7 +6623,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -6822,7 +6711,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S71" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6835,7 +6723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S87"/>
+  <dimension ref="A1:R87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6856,7 +6744,6 @@
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="4" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6950,11 +6837,6 @@
           <t>诅咒</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>应对方式</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -7039,11 +6921,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -7128,11 +7005,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -7217,7 +7089,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -7302,11 +7173,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -7391,7 +7257,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -7476,7 +7341,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -7561,7 +7425,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -7646,7 +7509,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -7731,7 +7593,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -7816,7 +7677,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -7901,7 +7761,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -7986,7 +7845,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -8071,7 +7929,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -8156,7 +8013,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -8241,7 +8097,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -8326,11 +8181,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -8415,7 +8265,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -8500,7 +8349,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -8585,7 +8433,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -8670,7 +8517,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -8755,7 +8601,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -8840,7 +8685,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -8925,7 +8769,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -9010,7 +8853,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -9095,7 +8937,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -9180,11 +9021,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -9269,7 +9105,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -9354,7 +9189,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -9439,7 +9273,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -9524,7 +9357,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -9609,7 +9441,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -9694,7 +9525,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -9779,7 +9609,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -9864,7 +9693,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -9949,7 +9777,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -10034,7 +9861,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -10119,7 +9945,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -10204,7 +10029,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -10289,7 +10113,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -10374,7 +10197,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -10459,7 +10281,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -10544,7 +10365,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -10629,7 +10449,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -10714,7 +10533,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -10799,7 +10617,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -10884,7 +10701,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -10969,7 +10785,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -11054,7 +10869,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -11139,7 +10953,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -11224,7 +11037,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -11309,7 +11121,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -11394,7 +11205,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -11479,7 +11289,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -11564,7 +11373,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -11649,7 +11457,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -11734,7 +11541,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11819,7 +11625,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11904,7 +11709,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11989,7 +11793,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -12074,7 +11877,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -12159,7 +11961,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -12244,7 +12045,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12329,7 +12129,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12414,7 +12213,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12499,7 +12297,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12584,7 +12381,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12669,7 +12465,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12754,7 +12549,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12839,7 +12633,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12924,7 +12717,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13009,7 +12801,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13094,7 +12885,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13179,7 +12969,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13264,7 +13053,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13349,7 +13137,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13434,7 +13221,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13519,7 +13305,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -13604,7 +13389,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -13689,7 +13473,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -13774,7 +13557,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -13859,7 +13641,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -13944,7 +13725,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14029,7 +13809,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -14114,7 +13893,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -14199,7 +13977,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -14284,7 +14061,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S87" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14297,7 +14073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S104"/>
+  <dimension ref="A1:R104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14318,7 +14094,6 @@
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="4" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14412,11 +14187,6 @@
           <t>诅咒</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>应对方式</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -14501,11 +14271,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>注意激怒（可安抚）</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -14590,7 +14355,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -14675,7 +14439,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -14760,7 +14523,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -14845,11 +14607,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -14934,7 +14691,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -15019,7 +14775,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -15104,7 +14859,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -15189,11 +14943,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -15278,11 +15027,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -15367,7 +15111,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -15452,7 +15195,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -15537,7 +15279,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -15622,7 +15363,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -15707,7 +15447,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -15792,7 +15531,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -15877,7 +15615,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -15962,7 +15699,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -16047,7 +15783,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -16132,7 +15867,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -16217,7 +15951,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -16302,11 +16035,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -16391,7 +16119,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -16476,7 +16203,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -16561,7 +16287,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -16646,7 +16371,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -16731,7 +16455,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -16816,7 +16539,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -16901,11 +16623,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -16990,7 +16707,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -17075,7 +16791,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -17160,7 +16875,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -17245,7 +16959,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -17330,11 +17043,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -17419,7 +17127,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -17504,7 +17211,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -17589,7 +17295,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -17674,7 +17379,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -17759,7 +17463,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -17844,7 +17547,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -17929,7 +17631,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -18014,11 +17715,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -18103,7 +17799,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -18188,7 +17883,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -18273,7 +17967,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -18358,7 +18051,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -18443,7 +18135,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -18528,7 +18219,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -18613,7 +18303,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -18698,7 +18387,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -18783,7 +18471,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -18868,11 +18555,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>注意流血（可驱散）</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -18957,7 +18639,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -19042,11 +18723,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S55" s="2" t="inlineStr">
-        <is>
-          <t>注意疾病（可驱散）</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -19131,7 +18807,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -19216,7 +18891,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -19301,7 +18975,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -19386,7 +19059,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -19471,7 +19143,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -19556,7 +19227,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -19641,7 +19311,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -19726,11 +19395,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S63" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -19815,7 +19479,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -19900,7 +19563,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -19985,7 +19647,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -20070,7 +19731,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -20155,7 +19815,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -20240,7 +19899,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -20325,7 +19983,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -20410,7 +20067,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -20495,7 +20151,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -20580,7 +20235,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -20665,7 +20319,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -20750,7 +20403,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -20835,7 +20487,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -20920,7 +20571,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -21005,7 +20655,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -21090,7 +20739,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -21175,7 +20823,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -21260,7 +20907,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -21345,7 +20991,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -21430,7 +21075,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -21515,7 +21159,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -21600,7 +21243,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -21685,7 +21327,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -21770,7 +21411,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -21855,7 +21495,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -21940,7 +21579,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -22025,7 +21663,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -22110,7 +21747,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -22195,7 +21831,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -22280,7 +21915,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -22365,7 +21999,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -22450,7 +22083,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -22535,7 +22167,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -22620,7 +22251,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -22705,7 +22335,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -22790,7 +22419,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -22875,11 +22503,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S100" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -22964,7 +22587,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -23049,7 +22671,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -23134,7 +22755,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -23219,7 +22839,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S104" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23232,7 +22851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S118"/>
+  <dimension ref="A1:R118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23253,7 +22872,6 @@
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="4" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23347,11 +22965,6 @@
           <t>诅咒</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>应对方式</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -23436,7 +23049,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -23521,7 +23133,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -23606,7 +23217,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -23691,7 +23301,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -23776,7 +23385,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -23861,7 +23469,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -23946,7 +23553,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -24031,7 +23637,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -24116,7 +23721,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -24201,11 +23805,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -24290,7 +23889,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -24375,7 +23973,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -24460,7 +24057,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -24545,7 +24141,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -24630,7 +24225,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -24715,7 +24309,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -24800,7 +24393,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -24885,11 +24477,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -24974,7 +24561,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -25059,7 +24645,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -25144,7 +24729,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -25229,7 +24813,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -25314,7 +24897,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -25399,7 +24981,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -25484,11 +25065,6 @@
           <t>是</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>注意诅咒（可驱散）</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -25573,7 +25149,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -25658,7 +25233,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -25743,7 +25317,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -25828,7 +25401,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -25913,7 +25485,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -25998,7 +25569,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -26083,7 +25653,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -26168,7 +25737,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -26253,7 +25821,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -26338,7 +25905,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -26423,7 +25989,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -26508,7 +26073,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -26593,7 +26157,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -26678,11 +26241,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -26767,7 +26325,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -26848,7 +26405,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -26933,11 +26489,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>注意恐惧</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -27022,7 +26573,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -27107,7 +26657,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -27192,7 +26741,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -27277,7 +26825,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -27362,7 +26909,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -27447,7 +26993,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -27532,7 +27077,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -27617,7 +27161,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -27702,7 +27245,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -27787,7 +27329,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -27872,7 +27413,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -27957,7 +27497,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -28042,7 +27581,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -28127,7 +27665,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -28212,11 +27749,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S58" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -28301,7 +27833,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -28386,7 +27917,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -28471,7 +28001,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -28556,7 +28085,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -28641,7 +28169,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -28726,7 +28253,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -28811,7 +28337,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -28896,7 +28421,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -28981,7 +28505,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -29066,7 +28589,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -29151,7 +28673,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -29236,7 +28757,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -29321,7 +28841,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -29406,7 +28925,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -29491,7 +29009,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -29576,7 +29093,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -29661,7 +29177,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -29746,7 +29261,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -29831,7 +29345,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -29916,7 +29429,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -30001,7 +29513,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -30086,7 +29597,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -30171,7 +29681,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -30256,7 +29765,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -30341,7 +29849,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -30426,7 +29933,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -30511,7 +30017,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -30596,7 +30101,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -30681,7 +30185,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -30766,7 +30269,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -30851,7 +30353,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -30936,7 +30437,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -31021,7 +30521,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -31106,7 +30605,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -31191,7 +30689,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -31276,7 +30773,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -31361,7 +30857,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -31446,7 +30941,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -31531,7 +31025,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -31616,7 +31109,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -31701,7 +31193,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -31786,7 +31277,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -31871,11 +31361,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S101" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -31960,7 +31445,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -32045,7 +31529,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -32130,7 +31613,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -32215,11 +31697,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S105" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -32304,7 +31781,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -32389,7 +31865,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -32474,7 +31949,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -32559,7 +32033,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -32644,7 +32117,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -32729,7 +32201,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -32814,7 +32285,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -32899,7 +32369,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -32984,7 +32453,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -33069,7 +32537,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -33154,7 +32621,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -33239,7 +32705,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -33324,7 +32789,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S118" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -33337,7 +32801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S74"/>
+  <dimension ref="A1:R74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -33358,7 +32822,6 @@
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="4" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33452,11 +32915,6 @@
           <t>诅咒</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>应对方式</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -33541,7 +32999,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -33626,7 +33083,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -33711,7 +33167,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -33796,7 +33251,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -33881,11 +33335,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -33970,11 +33419,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -34059,7 +33503,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -34144,11 +33587,6 @@
           <t>是</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>注意诅咒（可驱散）</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -34233,7 +33671,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -34318,7 +33755,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -34403,7 +33839,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -34488,7 +33923,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -34573,11 +34007,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -34662,11 +34091,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>注意疾病（可驱散）</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -34751,7 +34175,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -34836,7 +34259,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -34921,7 +34343,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -35006,7 +34427,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -35091,7 +34511,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -35176,7 +34595,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -35261,11 +34679,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -35350,7 +34763,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -35435,7 +34847,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -35520,11 +34931,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>注意激怒（可安抚）</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -35609,7 +35015,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -35694,7 +35099,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -35779,7 +35183,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -35864,11 +35267,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -35953,7 +35351,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -36038,7 +35435,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -36123,7 +35519,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -36208,7 +35603,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -36293,7 +35687,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -36378,7 +35771,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -36463,7 +35855,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -36548,7 +35939,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -36633,7 +36023,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -36718,11 +36107,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -36807,7 +36191,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -36892,7 +36275,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -36977,7 +36359,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -37062,7 +36443,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -37147,7 +36527,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -37232,7 +36611,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -37317,7 +36695,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -37402,7 +36779,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -37487,7 +36863,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -37572,7 +36947,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -37657,7 +37031,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -37742,7 +37115,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -37827,7 +37199,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -37912,7 +37283,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -37997,7 +37367,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -38082,7 +37451,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -38167,7 +37535,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -38252,7 +37619,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -38337,7 +37703,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -38422,7 +37787,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -38507,7 +37871,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -38592,7 +37955,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -38677,7 +38039,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -38762,7 +38123,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -38847,7 +38207,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -38932,7 +38291,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -39017,7 +38375,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -39102,7 +38459,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -39187,7 +38543,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -39272,7 +38627,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -39357,7 +38711,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -39442,11 +38795,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S71" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -39531,7 +38879,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -39616,11 +38963,6 @@
           <t>是</t>
         </is>
       </c>
-      <c r="S73" s="2" t="inlineStr">
-        <is>
-          <t>打断;注意诅咒（可驱散）</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -39705,7 +39047,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S74" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -39718,7 +39059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S74"/>
+  <dimension ref="A1:R74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -39739,7 +39080,6 @@
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="4" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39833,11 +39173,6 @@
           <t>诅咒</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>应对方式</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -39922,7 +39257,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -40007,7 +39341,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -40092,7 +39425,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -40177,7 +39509,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -40262,7 +39593,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -40347,7 +39677,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -40432,7 +39761,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -40517,7 +39845,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -40602,7 +39929,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -40687,11 +40013,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -40776,7 +40097,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -40861,7 +40181,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -40946,7 +40265,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -41031,7 +40349,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -41116,11 +40433,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -41205,7 +40517,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -41290,7 +40601,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -41375,7 +40685,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -41460,7 +40769,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -41545,7 +40853,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -41630,7 +40937,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -41715,11 +41021,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -41804,7 +41105,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -41889,7 +41189,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -41974,7 +41273,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -42059,7 +41357,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -42144,7 +41441,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -42229,7 +41525,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -42314,7 +41609,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -42399,7 +41693,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -42484,7 +41777,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -42569,7 +41861,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -42654,7 +41945,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -42739,7 +42029,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -42824,7 +42113,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -42909,7 +42197,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -42994,7 +42281,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -43079,7 +42365,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -43164,7 +42449,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -43249,7 +42533,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -43334,11 +42617,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>注意流血（可驱散）</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -43423,7 +42701,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -43508,7 +42785,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -43593,7 +42869,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -43678,7 +42953,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -43763,7 +43037,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -43848,11 +43121,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>注意激怒（可安抚）</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -43937,11 +43205,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -44026,7 +43289,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -44111,11 +43373,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -44200,7 +43457,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -44285,7 +43541,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -44370,7 +43625,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -44455,7 +43709,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -44540,7 +43793,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -44625,7 +43877,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -44710,7 +43961,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -44795,7 +44045,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -44880,7 +44129,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -44965,7 +44213,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -45050,7 +44297,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -45135,7 +44381,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -45220,7 +44465,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -45305,7 +44549,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -45390,7 +44633,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -45475,7 +44717,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -45560,7 +44801,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -45645,7 +44885,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -45730,7 +44969,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -45815,7 +45053,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -45900,7 +45137,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -45985,11 +45221,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S73" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -46074,7 +45305,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S74" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -46087,7 +45317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S67"/>
+  <dimension ref="A1:R67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -46108,7 +45338,6 @@
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="4" customWidth="1" min="18" max="18"/>
-    <col width="52" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -46202,11 +45431,6 @@
           <t>诅咒</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>应对方式</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -46291,7 +45515,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -46376,11 +45599,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -46465,7 +45683,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -46550,7 +45767,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -46635,11 +45851,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>注意激怒（可安抚）</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -46724,7 +45935,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -46809,7 +46019,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -46894,11 +46103,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -46983,7 +46187,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -47068,11 +46271,6 @@
           <t>是</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>打断;注意激怒（可安抚）;注意流血（可驱散）;注意中毒（可驱散）;注意疾病（可驱散）;注意诅咒（可驱散）</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -47157,7 +46355,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -47242,7 +46439,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -47327,7 +46523,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -47412,7 +46607,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -47497,7 +46691,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -47582,7 +46775,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -47667,7 +46859,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -47752,7 +46943,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -47837,7 +47027,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -47922,7 +47111,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -48007,7 +47195,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -48092,7 +47279,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -48177,7 +47363,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -48262,7 +47447,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -48347,7 +47531,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -48432,7 +47615,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -48517,7 +47699,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -48602,7 +47783,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -48687,7 +47867,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -48772,7 +47951,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -48857,7 +48035,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -48942,7 +48119,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -49027,7 +48203,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -49112,7 +48287,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -49197,7 +48371,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -49282,7 +48455,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -49367,7 +48539,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -49452,7 +48623,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -49537,7 +48707,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -49622,7 +48791,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -49707,7 +48875,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -49792,7 +48959,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -49877,7 +49043,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -49962,7 +49127,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -50047,7 +49211,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -50132,7 +49295,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -50217,7 +49379,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -50302,7 +49463,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -50387,7 +49547,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -50472,7 +49631,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -50557,7 +49715,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -50642,7 +49799,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -50727,7 +49883,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -50812,7 +49967,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -50897,7 +50051,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -50982,7 +50135,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -51067,11 +50219,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S58" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -51156,7 +50303,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -51241,7 +50387,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -51326,7 +50471,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -51411,7 +50555,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -51496,7 +50639,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -51581,7 +50723,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -51666,7 +50807,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -51751,7 +50891,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -51836,7 +50975,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S67" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -51849,7 +50987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S111"/>
+  <dimension ref="A1:R111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -51870,7 +51008,6 @@
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="4" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -51964,11 +51101,6 @@
           <t>诅咒</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>应对方式</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -52053,11 +51185,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -52142,7 +51269,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -52227,7 +51353,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -52312,7 +51437,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -52397,7 +51521,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -52482,7 +51605,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -52567,7 +51689,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -52652,7 +51773,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -52737,7 +51857,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -52822,7 +51941,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -52907,7 +52025,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -52992,11 +52109,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -53081,11 +52193,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>注意中毒（可驱散）</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -53170,7 +52277,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -53255,7 +52361,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -53340,7 +52445,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -53425,11 +52529,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -53514,11 +52613,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -53603,7 +52697,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -53688,7 +52781,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -53773,7 +52865,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -53858,7 +52949,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -53943,7 +53033,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -54028,7 +53117,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -54113,7 +53201,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -54198,7 +53285,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -54283,7 +53369,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -54368,7 +53453,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -54453,7 +53537,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -54538,11 +53621,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>注意中毒（可驱散）</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -54627,7 +53705,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -54712,11 +53789,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>注意流血（可驱散）</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -54801,7 +53873,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -54886,7 +53957,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -54971,7 +54041,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -55056,11 +54125,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -55145,7 +54209,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -55230,7 +54293,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -55315,7 +54377,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -55400,7 +54461,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -55485,7 +54545,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -55570,7 +54629,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -55655,7 +54713,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -55740,11 +54797,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>注意流血（可驱散）</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -55829,7 +54881,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -55914,7 +54965,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -55999,11 +55049,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>注意流血（可驱散）</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -56088,11 +55133,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>注意激怒（可安抚）</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -56177,11 +55217,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -56266,7 +55301,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -56351,7 +55385,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -56436,7 +55469,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -56521,7 +55553,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -56606,7 +55637,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -56691,7 +55721,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -56776,7 +55805,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -56861,7 +55889,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -56946,7 +55973,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -57031,7 +56057,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -57116,11 +56141,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S61" s="2" t="inlineStr">
-        <is>
-          <t>打断</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -57205,7 +56225,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -57290,7 +56309,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -57375,7 +56393,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -57460,7 +56477,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -57545,7 +56561,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -57630,7 +56645,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -57715,7 +56729,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -57800,7 +56813,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -57885,7 +56897,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -57970,7 +56981,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -58055,7 +57065,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -58140,7 +57149,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -58225,7 +57233,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -58310,7 +57317,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -58395,7 +57401,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -58480,7 +57485,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -58565,7 +57569,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -58650,7 +57653,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -58735,7 +57737,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -58820,7 +57821,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -58905,7 +57905,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -58990,7 +57989,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -59075,7 +58073,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -59160,7 +58157,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -59245,7 +58241,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -59330,7 +58325,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -59415,7 +58409,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -59500,7 +58493,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -59585,7 +58577,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -59670,7 +58661,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -59755,7 +58745,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -59840,7 +58829,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -59925,7 +58913,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -60010,7 +58997,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -60095,7 +59081,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -60180,7 +59165,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -60265,7 +59249,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -60350,7 +59333,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -60435,7 +59417,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -60520,7 +59501,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -60605,7 +59585,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -60690,7 +59669,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -60775,7 +59753,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -60860,7 +59837,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -60945,7 +59921,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -61030,7 +60005,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -61115,7 +60089,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -61200,7 +60173,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -61285,7 +60257,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -61370,7 +60341,6 @@
           <t>否</t>
         </is>
       </c>
-      <c r="S111" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
